--- a/MenuMasterData.xlsx
+++ b/MenuMasterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosaKaithakkod\Downloads\My Files\My Files\Rashid bro Menu web app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB5865E-B06F-43A7-B155-B7BF0AA1ADED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BBC7B4D-F3E0-4D06-8FDD-96249603AE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{58AFDDBF-ED6D-4E39-B166-E94F41C27959}"/>
   </bookViews>
   <sheets>
     <sheet name="Branding" sheetId="1" r:id="rId1"/>
@@ -3280,7 +3280,7 @@
         <v>131</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.55000000000000004">
